--- a/fapiao-templates/xinyuan_ca.xlsx
+++ b/fapiao-templates/xinyuan_ca.xlsx
@@ -10,10 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packing List装箱单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial Invoice发票" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlfn_DISPIMG" hidden="0" function="0" vbProcedure="0">none</definedName>
-    <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0" hidden="0" function="0" vbProcedure="0">'Packing List装箱单'!$A$2:$E$18</definedName>
-  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
